--- a/data_raw/re_A0309_商品房销售面积_万平方米.xlsx
+++ b/data_raw/re_A0309_商品房销售面积_万平方米.xlsx
@@ -1,216 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>商品房销售面积(万平方米)</t>
-  </si>
-  <si>
-    <t>上海</t>
-  </si>
-  <si>
-    <t>乌鲁木齐</t>
-  </si>
-  <si>
-    <t>兰州</t>
-  </si>
-  <si>
-    <t>北京</t>
-  </si>
-  <si>
-    <t>南京</t>
-  </si>
-  <si>
-    <t>南宁</t>
-  </si>
-  <si>
-    <t>南昌</t>
-  </si>
-  <si>
-    <t>厦门</t>
-  </si>
-  <si>
-    <t>合肥</t>
-  </si>
-  <si>
-    <t>呼和浩特</t>
-  </si>
-  <si>
-    <t>哈尔滨</t>
-  </si>
-  <si>
-    <t>大连</t>
-  </si>
-  <si>
-    <t>天津</t>
-  </si>
-  <si>
-    <t>太原</t>
-  </si>
-  <si>
-    <t>宁波</t>
-  </si>
-  <si>
-    <t>广州</t>
-  </si>
-  <si>
-    <t>成都</t>
-  </si>
-  <si>
-    <t>拉萨</t>
-  </si>
-  <si>
-    <t>昆明</t>
-  </si>
-  <si>
-    <t>杭州</t>
-  </si>
-  <si>
-    <t>武汉</t>
-  </si>
-  <si>
-    <t>沈阳</t>
-  </si>
-  <si>
-    <t>济南</t>
-  </si>
-  <si>
-    <t>海口</t>
-  </si>
-  <si>
-    <t>深圳</t>
-  </si>
-  <si>
-    <t>石家庄</t>
-  </si>
-  <si>
-    <t>福州</t>
-  </si>
-  <si>
-    <t>西宁</t>
-  </si>
-  <si>
-    <t>西安</t>
-  </si>
-  <si>
-    <t>贵阳</t>
-  </si>
-  <si>
-    <t>郑州</t>
-  </si>
-  <si>
-    <t>重庆</t>
-  </si>
-  <si>
-    <t>银川</t>
-  </si>
-  <si>
-    <t>长春</t>
-  </si>
-  <si>
-    <t>长沙</t>
-  </si>
-  <si>
-    <t>青岛</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -225,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -541,2251 +420,2424 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>商品房销售面积(万平方米)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>3025.4003</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>3694.9578</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>2339.29</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>3372.45</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>2060.96</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>1790.8598</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>1898.459</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>2382.2014</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>2084.6637</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>2431.3599</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>2705.6889</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>1691.6016</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>1767.01</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>1696.3432</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>1789.1616</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>1880.4536</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>1852.8837</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>1811.7051</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>1656.8637</v>
       </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3">
+      <c r="U2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>乌鲁木齐</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>413.4524</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>498.6926</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>296.1</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>537.27</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>444.61</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>465.8373</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>371.6101</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>535.6684</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>461.7934</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>524.956</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>582.0042999999999</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>606.9361</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>605.3038</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>657.4153</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>716.0853</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>764.1568</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>449.4284</v>
       </c>
-      <c r="S3">
+      <c r="S3" t="n">
         <v>548.9991</v>
       </c>
-      <c r="T3">
+      <c r="T3" t="n">
         <v>409.0074</v>
       </c>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4">
+      <c r="U3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>208.6341</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>268.9835</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>140.17</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>244.03</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>228.21</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>131.0912</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>190.3502</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>253.4619</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>480.3586</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>628.123</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>828.7934</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>697.9254</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>642.4213999999999</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>718.4354</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>846.4769</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>799.5752</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>282.2336</v>
       </c>
-      <c r="S4">
+      <c r="S4" t="n">
         <v>335.7544</v>
       </c>
-      <c r="T4">
+      <c r="T4" t="n">
         <v>305.7469</v>
       </c>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5">
+      <c r="U4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>2607.6178</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>2176.5727</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>1335.37</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>2362.25</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>1639.53</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>1439.2018</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>1943.7367</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>1903.1124</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>1454.1935</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>1554.2463</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>1658.9346</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>869.9521</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>696.1905</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>938.8623</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>970.8776</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>1107.0675</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>1039.9814</v>
       </c>
-      <c r="S5">
+      <c r="S5" t="n">
         <v>1131.817</v>
       </c>
-      <c r="T5">
+      <c r="T5" t="n">
         <v>1118.6514</v>
       </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6">
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>1010.5046</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>1137.879</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>703.55</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>1186.94</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>823.17</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>767.7073</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>950.8665</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>1222.0131</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>1207.5786</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>1543.1556</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>1558.1836</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>1429.6091</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>1220.7322</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>1320.6462</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>1324.672</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>1510.9536</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>942.3234</v>
       </c>
-      <c r="S6">
+      <c r="S6" t="n">
         <v>906.7683</v>
       </c>
-      <c r="T6">
+      <c r="T6" t="n">
         <v>930.12</v>
       </c>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7">
+      <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>南宁</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>456.0047</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>628.8407999999999</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>497.23</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>731.74</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>669.4</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>711.7298</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>629.0137</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>702.6007</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>802.5713</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>1000.7283</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>1327.5262</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>1544.1267</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>1745.1911</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>1805.2331</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>1837.5858</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>1494.0807</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>1324.7227</v>
       </c>
-      <c r="S7">
+      <c r="S7" t="n">
         <v>952.2263</v>
       </c>
-      <c r="T7">
+      <c r="T7" t="n">
         <v>807.3805</v>
       </c>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8">
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>383.5094</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>478.9932</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>335.48</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>494.69</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>520.84</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>499.1348</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>689.8563</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>841.4924</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>824.663</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>901.0158</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>1244.6529</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>1610.4283</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>1846.3065</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>1906.1278</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>1770.8267</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>2019.4934</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>1390.7026</v>
       </c>
-      <c r="S8">
+      <c r="S8" t="n">
         <v>717.7742</v>
       </c>
-      <c r="T8">
+      <c r="T8" t="n">
         <v>690.0463999999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>厦门</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>433.2666</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>497.7011</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>389.47</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>529.29</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>426.77</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>445.3899</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>615.3434999999999</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>786.7109</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>790.2089999999999</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>570.8332</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>528.8601</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>527.8806</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>529.4175</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>540.7725</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>621.8152</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>593.0386999999999</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>607.6323</v>
       </c>
-      <c r="S9">
+      <c r="S9" t="n">
         <v>603.7939</v>
       </c>
-      <c r="T9">
+      <c r="T9" t="n">
         <v>484.6798</v>
       </c>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10">
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>650.3107</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>1042.6878</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>933.13</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>1297.95</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>1004.7</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>1245.9761</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>1242.4768</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>1628.0937</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>1594.7869</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>1589.2069</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>2098.3411</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>1283.3996</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>1389.5794</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>1321.872</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>1486.1077</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>1836.5887</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>1459.1789</v>
       </c>
-      <c r="S10">
+      <c r="S10" t="n">
         <v>1109.2544</v>
       </c>
-      <c r="T10">
+      <c r="T10" t="n">
         <v>974.0326</v>
       </c>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11">
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>215.3219</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>225.8929</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>331.89</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>379.58</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>471.88</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>449.7116</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>478.1847</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>420.4521</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>363.9075</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>381.8083</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>425.493</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>316.5095</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>396.0464</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>325.9983</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>413.7646</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>309.6567</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>145.8349</v>
       </c>
-      <c r="S11">
+      <c r="S11" t="n">
         <v>187.7909</v>
       </c>
-      <c r="T11">
+      <c r="T11" t="n">
         <v>186.0994</v>
       </c>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12">
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>674.4077</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>748.9494999999999</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>587.08</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>705.28</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>881.75</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>998.5876</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>1195.2816</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>1370.4803</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>1041.0546</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>895.9832</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>1057.9642</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>1269.5403</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>1050.5767</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>964.7782999999999</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>768.5029</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>609.4453999999999</v>
       </c>
-      <c r="R12">
+      <c r="R12" t="n">
         <v>408.971</v>
       </c>
-      <c r="S12">
+      <c r="S12" t="n">
         <v>388.6454</v>
       </c>
-      <c r="T12">
+      <c r="T12" t="n">
         <v>313.8561</v>
       </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13">
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>大连</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>628.7834</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>828.2375</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>822.71</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>1152.68</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>1215.33</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>909.9105</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>1076.3624</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>1222.125</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>746.4018</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>637.3329</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>707.4894</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>839.8366</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>775.9450000000001</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>658.8721</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>714.8425999999999</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>687.7109</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>434.327</v>
       </c>
-      <c r="S13">
+      <c r="S13" t="n">
         <v>309.0346</v>
       </c>
-      <c r="T13">
+      <c r="T13" t="n">
         <v>292.7222</v>
       </c>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14">
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>1458.5984</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>1548.5931</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>1252.04</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>1590.02</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>1514.52</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>1594.5695</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="n">
         <v>1661.6941</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="n">
         <v>1847.1121</v>
       </c>
-      <c r="J14">
+      <c r="J14" t="n">
         <v>1612.9827</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="n">
         <v>1771.0706</v>
       </c>
-      <c r="L14">
+      <c r="L14" t="n">
         <v>2711.0848</v>
       </c>
-      <c r="M14">
+      <c r="M14" t="n">
         <v>1482.1233</v>
       </c>
-      <c r="N14">
+      <c r="N14" t="n">
         <v>1249.869</v>
       </c>
-      <c r="O14">
+      <c r="O14" t="n">
         <v>1478.6795</v>
       </c>
-      <c r="P14">
+      <c r="P14" t="n">
         <v>1306.9574</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" t="n">
         <v>1435.4193</v>
       </c>
-      <c r="R14">
+      <c r="R14" t="n">
         <v>973.7713</v>
       </c>
-      <c r="S14">
+      <c r="S14" t="n">
         <v>1178.5072</v>
       </c>
-      <c r="T14">
+      <c r="T14" t="n">
         <v>1183.8126</v>
       </c>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15">
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>137.2342</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>167.2269</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>182.94</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>183.8</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>258.82</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>216.1778</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="n">
         <v>324.8146</v>
       </c>
-      <c r="I15">
+      <c r="I15" t="n">
         <v>423.3146</v>
       </c>
-      <c r="J15">
+      <c r="J15" t="n">
         <v>419.2118</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="n">
         <v>448.2833</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="n">
         <v>609.8354</v>
       </c>
-      <c r="M15">
+      <c r="M15" t="n">
         <v>786.4129</v>
       </c>
-      <c r="N15">
+      <c r="N15" t="n">
         <v>839.4204</v>
       </c>
-      <c r="O15">
+      <c r="O15" t="n">
         <v>741.0956</v>
       </c>
-      <c r="P15">
+      <c r="P15" t="n">
         <v>781.3624</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" t="n">
         <v>821.7802</v>
       </c>
-      <c r="R15">
+      <c r="R15" t="n">
         <v>507.3695</v>
       </c>
-      <c r="S15">
+      <c r="S15" t="n">
         <v>532.7752</v>
       </c>
-      <c r="T15">
+      <c r="T15" t="n">
         <v>399.0143</v>
       </c>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16">
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>609.3136</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>804.4283</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>448.38</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>815.1799999999999</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>693.5599999999999</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>526.5287</v>
       </c>
-      <c r="H16">
+      <c r="H16" t="n">
         <v>590.2173</v>
       </c>
-      <c r="I16">
+      <c r="I16" t="n">
         <v>730.0878</v>
       </c>
-      <c r="J16">
+      <c r="J16" t="n">
         <v>726.4365</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="n">
         <v>1007.2086</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="n">
         <v>1336.9494</v>
       </c>
-      <c r="M16">
+      <c r="M16" t="n">
         <v>1543.6443</v>
       </c>
-      <c r="N16">
+      <c r="N16" t="n">
         <v>1624.3772</v>
       </c>
-      <c r="O16">
+      <c r="O16" t="n">
         <v>1714.6361</v>
       </c>
-      <c r="P16">
+      <c r="P16" t="n">
         <v>1858.1974</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" t="n">
         <v>1606.2277</v>
       </c>
-      <c r="R16">
+      <c r="R16" t="n">
         <v>1128.796</v>
       </c>
-      <c r="S16">
+      <c r="S16" t="n">
         <v>901.5601</v>
       </c>
-      <c r="T16">
+      <c r="T16" t="n">
         <v>796.265</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17">
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>1316.8842</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>1351.3323</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>1024.96</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>1375.42</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>1405.13</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>1194.0755</v>
       </c>
-      <c r="H17">
+      <c r="H17" t="n">
         <v>1333.1259</v>
       </c>
-      <c r="I17">
+      <c r="I17" t="n">
         <v>1699.983</v>
       </c>
-      <c r="J17">
+      <c r="J17" t="n">
         <v>1540.0173</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="n">
         <v>1653.0655</v>
       </c>
-      <c r="L17">
+      <c r="L17" t="n">
         <v>1949.0982</v>
       </c>
-      <c r="M17">
+      <c r="M17" t="n">
         <v>1757.7529</v>
       </c>
-      <c r="N17">
+      <c r="N17" t="n">
         <v>1550.2761</v>
       </c>
-      <c r="O17">
+      <c r="O17" t="n">
         <v>1464.6364</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="n">
         <v>1539.4026</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" t="n">
         <v>1736.3064</v>
       </c>
-      <c r="R17">
+      <c r="R17" t="n">
         <v>1374.074</v>
       </c>
-      <c r="S17">
+      <c r="S17" t="n">
         <v>1404.4885</v>
       </c>
-      <c r="T17">
+      <c r="T17" t="n">
         <v>1159.2531</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18">
+      <c r="U17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>1590.5588</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>2225.5003</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>1459.5</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>2708.76</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>2559.28</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>2676.0384</v>
       </c>
-      <c r="H18">
+      <c r="H18" t="n">
         <v>2844.0887</v>
       </c>
-      <c r="I18">
+      <c r="I18" t="n">
         <v>2950.1333</v>
       </c>
-      <c r="J18">
+      <c r="J18" t="n">
         <v>2951.2999</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="n">
         <v>2997.4316</v>
       </c>
-      <c r="L18">
+      <c r="L18" t="n">
         <v>3928.768</v>
       </c>
-      <c r="M18">
+      <c r="M18" t="n">
         <v>3925.9098</v>
       </c>
-      <c r="N18">
+      <c r="N18" t="n">
         <v>3682.5236</v>
       </c>
-      <c r="O18">
+      <c r="O18" t="n">
         <v>3543.282</v>
       </c>
-      <c r="P18">
+      <c r="P18" t="n">
         <v>3680.2992</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" t="n">
         <v>3644.1101</v>
       </c>
-      <c r="R18">
+      <c r="R18" t="n">
         <v>2549.3975</v>
       </c>
-      <c r="S18">
+      <c r="S18" t="n">
         <v>2204.566</v>
       </c>
-      <c r="T18">
+      <c r="T18" t="n">
         <v>1968.1443</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
-      <c r="A19" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20">
+      <c r="U18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>拉萨</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>913.2992</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>928.8243</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>585.92</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>853.27</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>1241.01</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>1121.2957</v>
       </c>
-      <c r="H20">
+      <c r="H20" t="n">
         <v>1051.3532</v>
       </c>
-      <c r="I20">
+      <c r="I20" t="n">
         <v>1211.1969</v>
       </c>
-      <c r="J20">
+      <c r="J20" t="n">
         <v>1289.369</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="n">
         <v>1305.0282</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="n">
         <v>1520.8717</v>
       </c>
-      <c r="M20">
+      <c r="M20" t="n">
         <v>1827.2477</v>
       </c>
-      <c r="N20">
+      <c r="N20" t="n">
         <v>1909.7211</v>
       </c>
-      <c r="O20">
+      <c r="O20" t="n">
         <v>1916.2303</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="n">
         <v>1878.8049</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" t="n">
         <v>1297.5557</v>
       </c>
-      <c r="R20">
+      <c r="R20" t="n">
         <v>822.5038</v>
       </c>
-      <c r="S20">
+      <c r="S20" t="n">
         <v>749.4869</v>
       </c>
-      <c r="T20">
+      <c r="T20" t="n">
         <v>639.0170000000001</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21">
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>761.7613</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>1150.2833</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>775.02</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>1456.38</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>988.34</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>738.0377999999999</v>
       </c>
-      <c r="H21">
+      <c r="H21" t="n">
         <v>1089.6234</v>
       </c>
-      <c r="I21">
+      <c r="I21" t="n">
         <v>1139.1306</v>
       </c>
-      <c r="J21">
+      <c r="J21" t="n">
         <v>1122.9128</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="n">
         <v>1482.1676</v>
       </c>
-      <c r="L21">
+      <c r="L21" t="n">
         <v>2327.8649</v>
       </c>
-      <c r="M21">
+      <c r="M21" t="n">
         <v>2054.1135</v>
       </c>
-      <c r="N21">
+      <c r="N21" t="n">
         <v>1675.981</v>
       </c>
-      <c r="O21">
+      <c r="O21" t="n">
         <v>1513.6233</v>
       </c>
-      <c r="P21">
+      <c r="P21" t="n">
         <v>1699.3378</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" t="n">
         <v>2236.2478</v>
       </c>
-      <c r="R21">
+      <c r="R21" t="n">
         <v>1393.6603</v>
       </c>
-      <c r="S21">
+      <c r="S21" t="n">
         <v>1447.3419</v>
       </c>
-      <c r="T21">
+      <c r="T21" t="n">
         <v>1038.0589</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22">
+      <c r="U21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>960.8808</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>1135.4127</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>732.0700000000001</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>1086.99</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>1211.71</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>1329.3366</v>
       </c>
-      <c r="H22">
+      <c r="H22" t="n">
         <v>1576.1126</v>
       </c>
-      <c r="I22">
+      <c r="I22" t="n">
         <v>1995.3562</v>
       </c>
-      <c r="J22">
+      <c r="J22" t="n">
         <v>2273.1563</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="n">
         <v>2627.1872</v>
       </c>
-      <c r="L22">
+      <c r="L22" t="n">
         <v>3255.655</v>
       </c>
-      <c r="M22">
+      <c r="M22" t="n">
         <v>3532.6055</v>
       </c>
-      <c r="N22">
+      <c r="N22" t="n">
         <v>3646.9391</v>
       </c>
-      <c r="O22">
+      <c r="O22" t="n">
         <v>3332.3398</v>
       </c>
-      <c r="P22">
+      <c r="P22" t="n">
         <v>2646.3699</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" t="n">
         <v>2759.3911</v>
       </c>
-      <c r="R22">
+      <c r="R22" t="n">
         <v>2122.3352</v>
       </c>
-      <c r="S22">
+      <c r="S22" t="n">
         <v>1972.9609</v>
       </c>
-      <c r="T22">
+      <c r="T22" t="n">
         <v>1998.2954</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23">
+      <c r="U22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>1243.7888</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>1462.0429</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>1465.05</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>1532.93</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>1746.52</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>2165.165</v>
       </c>
-      <c r="H23">
+      <c r="H23" t="n">
         <v>2469.6526</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>2262.3264</v>
       </c>
-      <c r="J23">
+      <c r="J23" t="n">
         <v>1498.4012</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="n">
         <v>1065.0606</v>
       </c>
-      <c r="L23">
+      <c r="L23" t="n">
         <v>1184.3163</v>
       </c>
-      <c r="M23">
+      <c r="M23" t="n">
         <v>1300.2363</v>
       </c>
-      <c r="N23">
+      <c r="N23" t="n">
         <v>1354.8192</v>
       </c>
-      <c r="O23">
+      <c r="O23" t="n">
         <v>1453.5275</v>
       </c>
-      <c r="P23">
+      <c r="P23" t="n">
         <v>1381.3231</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" t="n">
         <v>1092.6978</v>
       </c>
-      <c r="R23">
+      <c r="R23" t="n">
         <v>648.8901</v>
       </c>
-      <c r="S23">
+      <c r="S23" t="n">
         <v>530.332</v>
       </c>
-      <c r="T23">
+      <c r="T23" t="n">
         <v>522.5655</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24">
+      <c r="U23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>284.655</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>320.2448</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>371.16</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>441.06</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>531.49</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>596.1735</v>
       </c>
-      <c r="H24">
+      <c r="H24" t="n">
         <v>659.5628</v>
       </c>
-      <c r="I24">
+      <c r="I24" t="n">
         <v>822.6254</v>
       </c>
-      <c r="J24">
+      <c r="J24" t="n">
         <v>865.3513</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="n">
         <v>1192.1174</v>
       </c>
-      <c r="L24">
+      <c r="L24" t="n">
         <v>1425.2878</v>
       </c>
-      <c r="M24">
+      <c r="M24" t="n">
         <v>1216.2717</v>
       </c>
-      <c r="N24">
+      <c r="N24" t="n">
         <v>1236.3036</v>
       </c>
-      <c r="O24">
+      <c r="O24" t="n">
         <v>1151.0047</v>
       </c>
-      <c r="P24">
+      <c r="P24" t="n">
         <v>1335.7486</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" t="n">
         <v>1548.1974</v>
       </c>
-      <c r="R24">
+      <c r="R24" t="n">
         <v>1241.9469</v>
       </c>
-      <c r="S24">
+      <c r="S24" t="n">
         <v>1170.2186</v>
       </c>
-      <c r="T24">
+      <c r="T24" t="n">
         <v>1036.2771</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25">
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>海口</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>141.6425</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>170.4645</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>176.29</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>191.78</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>209.76</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>221.8046</v>
       </c>
-      <c r="H25">
+      <c r="H25" t="n">
         <v>266.9509</v>
       </c>
-      <c r="I25">
+      <c r="I25" t="n">
         <v>338.1897</v>
       </c>
-      <c r="J25">
+      <c r="J25" t="n">
         <v>337.6632</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="n">
         <v>373.4021</v>
       </c>
-      <c r="L25">
+      <c r="L25" t="n">
         <v>432.7139</v>
       </c>
-      <c r="M25">
+      <c r="M25" t="n">
         <v>549.5948</v>
       </c>
-      <c r="N25">
+      <c r="N25" t="n">
         <v>393.3248</v>
       </c>
-      <c r="O25">
+      <c r="O25" t="n">
         <v>440.559</v>
       </c>
-      <c r="P25">
+      <c r="P25" t="n">
         <v>463.7355</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" t="n">
         <v>484.5977</v>
       </c>
-      <c r="R25">
+      <c r="R25" t="n">
         <v>269.4434</v>
       </c>
-      <c r="S25">
+      <c r="S25" t="n">
         <v>325.7905</v>
       </c>
-      <c r="T25">
+      <c r="T25" t="n">
         <v>381.1877</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
-      <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26">
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>749.0775</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>555.1102</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>466.71</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>762.15</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>465.59</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>496.889</v>
       </c>
-      <c r="H26">
+      <c r="H26" t="n">
         <v>525.8334</v>
       </c>
-      <c r="I26">
+      <c r="I26" t="n">
         <v>588.5819</v>
       </c>
-      <c r="J26">
+      <c r="J26" t="n">
         <v>532.5666</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="n">
         <v>831.4644</v>
       </c>
-      <c r="L26">
+      <c r="L26" t="n">
         <v>736.1932</v>
       </c>
-      <c r="M26">
+      <c r="M26" t="n">
         <v>671.033</v>
       </c>
-      <c r="N26">
+      <c r="N26" t="n">
         <v>722.0111000000001</v>
       </c>
-      <c r="O26">
+      <c r="O26" t="n">
         <v>806.5598</v>
       </c>
-      <c r="P26">
+      <c r="P26" t="n">
         <v>908.795</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" t="n">
         <v>799.5853</v>
       </c>
-      <c r="R26">
+      <c r="R26" t="n">
         <v>679.1094000000001</v>
       </c>
-      <c r="S26">
+      <c r="S26" t="n">
         <v>762.0038</v>
       </c>
-      <c r="T26">
+      <c r="T26" t="n">
         <v>828.667</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
-      <c r="A27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27">
+      <c r="U26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>303.5256</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>393.5803</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>338.86</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>349.76</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>469.31</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>922.2363</v>
       </c>
-      <c r="H27">
+      <c r="H27" t="n">
         <v>768.7331</v>
       </c>
-      <c r="I27">
+      <c r="I27" t="n">
         <v>951.2114</v>
       </c>
-      <c r="J27">
+      <c r="J27" t="n">
         <v>888.2583</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="n">
         <v>757.8159000000001</v>
       </c>
-      <c r="L27">
+      <c r="L27" t="n">
         <v>798.4168</v>
       </c>
-      <c r="M27">
+      <c r="M27" t="n">
         <v>1027.3362</v>
       </c>
-      <c r="N27">
+      <c r="N27" t="n">
         <v>844.6900000000001</v>
       </c>
-      <c r="O27">
+      <c r="O27" t="n">
         <v>782.2808</v>
       </c>
-      <c r="P27">
+      <c r="P27" t="n">
         <v>656.2621</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" t="n">
         <v>720.2925</v>
       </c>
-      <c r="R27">
+      <c r="R27" t="n">
         <v>606.0616</v>
       </c>
-      <c r="S27">
+      <c r="S27" t="n">
         <v>586.7506</v>
       </c>
-      <c r="T27">
+      <c r="T27" t="n">
         <v>490.5049</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
-      <c r="A28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28">
+      <c r="U27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
         <v>664.583</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>645.63</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>370.66</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>690.13</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>597.8</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>621.043</v>
       </c>
-      <c r="H28">
+      <c r="H28" t="n">
         <v>841.4981</v>
       </c>
-      <c r="I28">
+      <c r="I28" t="n">
         <v>1256.4926</v>
       </c>
-      <c r="J28">
+      <c r="J28" t="n">
         <v>965.5969</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="n">
         <v>914.7024</v>
       </c>
-      <c r="L28">
+      <c r="L28" t="n">
         <v>1221.3323</v>
       </c>
-      <c r="M28">
+      <c r="M28" t="n">
         <v>1685.4646</v>
       </c>
-      <c r="N28">
+      <c r="N28" t="n">
         <v>1711.0517</v>
       </c>
-      <c r="O28">
+      <c r="O28" t="n">
         <v>1708.1896</v>
       </c>
-      <c r="P28">
+      <c r="P28" t="n">
         <v>1888.1024</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" t="n">
         <v>2138.4859</v>
       </c>
-      <c r="R28">
+      <c r="R28" t="n">
         <v>1419.6992</v>
       </c>
-      <c r="S28">
+      <c r="S28" t="n">
         <v>877.4059</v>
       </c>
-      <c r="T28">
+      <c r="T28" t="n">
         <v>739.1464</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
-      <c r="A29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29">
+      <c r="U28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>西宁</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
         <v>106.4423</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>139.5479</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>108.31</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>154.68</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>217.1</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>265.6097</v>
       </c>
-      <c r="H29">
+      <c r="H29" t="n">
         <v>177.0355</v>
       </c>
-      <c r="I29">
+      <c r="I29" t="n">
         <v>277.7969</v>
       </c>
-      <c r="J29">
+      <c r="J29" t="n">
         <v>305.7114</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="n">
         <v>311.8641</v>
       </c>
-      <c r="L29">
+      <c r="L29" t="n">
         <v>352.6041</v>
       </c>
-      <c r="M29">
+      <c r="M29" t="n">
         <v>388.2192</v>
       </c>
-      <c r="N29">
+      <c r="N29" t="n">
         <v>332.2212</v>
       </c>
-      <c r="O29">
+      <c r="O29" t="n">
         <v>321.2388</v>
       </c>
-      <c r="P29">
+      <c r="P29" t="n">
         <v>298.9698</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" t="n">
         <v>226.6362</v>
       </c>
-      <c r="R29">
+      <c r="R29" t="n">
         <v>100.212</v>
       </c>
-      <c r="S29">
+      <c r="S29" t="n">
         <v>106.1535</v>
       </c>
-      <c r="T29">
+      <c r="T29" t="n">
         <v>104.5673</v>
       </c>
-    </row>
-    <row r="30" spans="1:20">
-      <c r="A30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30">
+      <c r="U29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
         <v>621.5019</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>833.9198</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>767.23</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>1256.02</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>1587.81</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="n">
         <v>1768.5175</v>
       </c>
-      <c r="H30">
+      <c r="H30" t="n">
         <v>1532.8991</v>
       </c>
-      <c r="I30">
+      <c r="I30" t="n">
         <v>1632.8496</v>
       </c>
-      <c r="J30">
+      <c r="J30" t="n">
         <v>1696.3881</v>
       </c>
-      <c r="K30">
+      <c r="K30" t="n">
         <v>1762.7011</v>
       </c>
-      <c r="L30">
+      <c r="L30" t="n">
         <v>2036.1819</v>
       </c>
-      <c r="M30">
+      <c r="M30" t="n">
         <v>2459.3495</v>
       </c>
-      <c r="N30">
+      <c r="N30" t="n">
         <v>2621.7177</v>
       </c>
-      <c r="O30">
+      <c r="O30" t="n">
         <v>2375.4062</v>
       </c>
-      <c r="P30">
+      <c r="P30" t="n">
         <v>2081.4796</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" t="n">
         <v>1492.9179</v>
       </c>
-      <c r="R30">
+      <c r="R30" t="n">
         <v>1382.7648</v>
       </c>
-      <c r="S30">
+      <c r="S30" t="n">
         <v>1265.3295</v>
       </c>
-      <c r="T30">
+      <c r="T30" t="n">
         <v>1208.3054</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
-      <c r="A31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31">
+      <c r="U30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>387.7157</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>439.2821</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>411.93</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>818.22</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>801.5599999999999</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="n">
         <v>807.5339</v>
       </c>
-      <c r="H31">
+      <c r="H31" t="n">
         <v>1023.837</v>
       </c>
-      <c r="I31">
+      <c r="I31" t="n">
         <v>1282.007</v>
       </c>
-      <c r="J31">
+      <c r="J31" t="n">
         <v>935.5458</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="n">
         <v>959.5491</v>
       </c>
-      <c r="L31">
+      <c r="L31" t="n">
         <v>981.8689000000001</v>
       </c>
-      <c r="M31">
+      <c r="M31" t="n">
         <v>1068.6715</v>
       </c>
-      <c r="N31">
+      <c r="N31" t="n">
         <v>1114.5588</v>
       </c>
-      <c r="O31">
+      <c r="O31" t="n">
         <v>1099.2659</v>
       </c>
-      <c r="P31">
+      <c r="P31" t="n">
         <v>1235.7462</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" t="n">
         <v>1407.5455</v>
       </c>
-      <c r="R31">
+      <c r="R31" t="n">
         <v>829.1414</v>
       </c>
-      <c r="S31">
+      <c r="S31" t="n">
         <v>478.2141</v>
       </c>
-      <c r="T31">
+      <c r="T31" t="n">
         <v>507.0667</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
-      <c r="A32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32">
+      <c r="U31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
         <v>800.8225</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>1097.895</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>736.85</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>1197.1</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>1558.72</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="n">
         <v>1563.2188</v>
       </c>
-      <c r="H32">
+      <c r="H32" t="n">
         <v>1441.869</v>
       </c>
-      <c r="I32">
+      <c r="I32" t="n">
         <v>1621.8948</v>
       </c>
-      <c r="J32">
+      <c r="J32" t="n">
         <v>1591.9073</v>
       </c>
-      <c r="K32">
+      <c r="K32" t="n">
         <v>1898.6666</v>
       </c>
-      <c r="L32">
+      <c r="L32" t="n">
         <v>2859.1803</v>
       </c>
-      <c r="M32">
+      <c r="M32" t="n">
         <v>3097.8112</v>
       </c>
-      <c r="N32">
+      <c r="N32" t="n">
         <v>3712.1143</v>
       </c>
-      <c r="O32">
+      <c r="O32" t="n">
         <v>3593.2689</v>
       </c>
-      <c r="P32">
+      <c r="P32" t="n">
         <v>3426.0594</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" t="n">
         <v>2699.3808</v>
       </c>
-      <c r="R32">
+      <c r="R32" t="n">
         <v>1999.3608</v>
       </c>
-      <c r="S32">
+      <c r="S32" t="n">
         <v>2027.797</v>
       </c>
-      <c r="T32">
+      <c r="T32" t="n">
         <v>1908.948</v>
       </c>
-    </row>
-    <row r="33" spans="1:20">
-      <c r="A33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33">
+      <c r="U32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>2228.4585</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>3552.9225</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>2872.19</v>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>4002.89</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>4314.39</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="n">
         <v>4533.5019</v>
       </c>
-      <c r="H33">
+      <c r="H33" t="n">
         <v>4522.3997</v>
       </c>
-      <c r="I33">
+      <c r="I33" t="n">
         <v>4817.5643</v>
       </c>
-      <c r="J33">
+      <c r="J33" t="n">
         <v>5100.387</v>
       </c>
-      <c r="K33">
+      <c r="K33" t="n">
         <v>5381.3726</v>
       </c>
-      <c r="L33">
+      <c r="L33" t="n">
         <v>6257.1463</v>
       </c>
-      <c r="M33">
+      <c r="M33" t="n">
         <v>6711.0048</v>
       </c>
-      <c r="N33">
+      <c r="N33" t="n">
         <v>6536.2487</v>
       </c>
-      <c r="O33">
+      <c r="O33" t="n">
         <v>6104.6831</v>
       </c>
-      <c r="P33">
+      <c r="P33" t="n">
         <v>6143.47</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" t="n">
         <v>6197.7061</v>
       </c>
-      <c r="R33">
+      <c r="R33" t="n">
         <v>4142.9249</v>
       </c>
-      <c r="S33">
+      <c r="S33" t="n">
         <v>3557.245</v>
       </c>
-      <c r="T33">
+      <c r="T33" t="n">
         <v>2980.1659</v>
       </c>
-    </row>
-    <row r="34" spans="1:20">
-      <c r="A34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34">
+      <c r="U33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
         <v>239.989</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>335.9689</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>307.73</v>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>511.43</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>590.04</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="n">
         <v>489.0287</v>
       </c>
-      <c r="H34">
+      <c r="H34" t="n">
         <v>450.261</v>
       </c>
-      <c r="I34">
+      <c r="I34" t="n">
         <v>612.1084</v>
       </c>
-      <c r="J34">
+      <c r="J34" t="n">
         <v>724.5852</v>
       </c>
-      <c r="K34">
+      <c r="K34" t="n">
         <v>529.806</v>
       </c>
-      <c r="L34">
+      <c r="L34" t="n">
         <v>564.8583</v>
       </c>
-      <c r="M34">
+      <c r="M34" t="n">
         <v>595.2162</v>
       </c>
-      <c r="N34">
+      <c r="N34" t="n">
         <v>612.8287</v>
       </c>
-      <c r="O34">
+      <c r="O34" t="n">
         <v>679.3824</v>
       </c>
-      <c r="P34">
+      <c r="P34" t="n">
         <v>751.7529</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" t="n">
         <v>641.5742</v>
       </c>
-      <c r="R34">
+      <c r="R34" t="n">
         <v>403.7083</v>
       </c>
-      <c r="S34">
+      <c r="S34" t="n">
         <v>350.85</v>
       </c>
-      <c r="T34">
+      <c r="T34" t="n">
         <v>262.7612</v>
       </c>
-    </row>
-    <row r="35" spans="1:20">
-      <c r="A35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35">
+      <c r="U34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
         <v>408.2532</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>513.7732</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>570.64</v>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>715.72</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>863.08</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="n">
         <v>879.1395</v>
       </c>
-      <c r="H35">
+      <c r="H35" t="n">
         <v>907.9951</v>
       </c>
-      <c r="I35">
+      <c r="I35" t="n">
         <v>847.0622</v>
       </c>
-      <c r="J35">
+      <c r="J35" t="n">
         <v>758.8363000000001</v>
       </c>
-      <c r="K35">
+      <c r="K35" t="n">
         <v>799.1167</v>
       </c>
-      <c r="L35">
+      <c r="L35" t="n">
         <v>1017.7486</v>
       </c>
-      <c r="M35">
+      <c r="M35" t="n">
         <v>1147.1891</v>
       </c>
-      <c r="N35">
+      <c r="N35" t="n">
         <v>1288.4445</v>
       </c>
-      <c r="O35">
+      <c r="O35" t="n">
         <v>1342.3696</v>
       </c>
-      <c r="P35">
+      <c r="P35" t="n">
         <v>1054.4128</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" t="n">
         <v>1027.2495</v>
       </c>
-      <c r="R35">
+      <c r="R35" t="n">
         <v>540.7714999999999</v>
       </c>
-      <c r="S35">
+      <c r="S35" t="n">
         <v>570.7406999999999</v>
       </c>
-      <c r="T35">
+      <c r="T35" t="n">
         <v>530.4050999999999</v>
       </c>
-    </row>
-    <row r="36" spans="1:20">
-      <c r="A36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36">
+      <c r="U35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
         <v>741.686</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>978.5585</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>858.74</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>1406.58</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>1680.21</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="n">
         <v>1508.1806</v>
       </c>
-      <c r="H36">
+      <c r="H36" t="n">
         <v>1526.9295</v>
       </c>
-      <c r="I36">
+      <c r="I36" t="n">
         <v>1861.5564</v>
       </c>
-      <c r="J36">
+      <c r="J36" t="n">
         <v>1518.4711</v>
       </c>
-      <c r="K36">
+      <c r="K36" t="n">
         <v>1907.9135</v>
       </c>
-      <c r="L36">
+      <c r="L36" t="n">
         <v>2613.2583</v>
       </c>
-      <c r="M36">
+      <c r="M36" t="n">
         <v>2260.7893</v>
       </c>
-      <c r="N36">
+      <c r="N36" t="n">
         <v>2386.7371</v>
       </c>
-      <c r="O36">
+      <c r="O36" t="n">
         <v>2335.1501</v>
       </c>
-      <c r="P36">
+      <c r="P36" t="n">
         <v>2377.4346</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" t="n">
         <v>2606.166</v>
       </c>
-      <c r="R36">
+      <c r="R36" t="n">
         <v>1699.3613</v>
       </c>
-      <c r="S36">
+      <c r="S36" t="n">
         <v>1556.7774</v>
       </c>
-      <c r="T36">
+      <c r="T36" t="n">
         <v>1356.802</v>
       </c>
-    </row>
-    <row r="37" spans="1:20">
-      <c r="A37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37">
+      <c r="U36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>718.4139</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>833.2905</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>770.3</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>1261.86</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>1360.69</v>
       </c>
-      <c r="G37">
+      <c r="G37" t="n">
         <v>1029.9105</v>
       </c>
-      <c r="H37">
+      <c r="H37" t="n">
         <v>950.9186999999999</v>
       </c>
-      <c r="I37">
+      <c r="I37" t="n">
         <v>1160.1552</v>
       </c>
-      <c r="J37">
+      <c r="J37" t="n">
         <v>1163.5302</v>
       </c>
-      <c r="K37">
+      <c r="K37" t="n">
         <v>1418.5845</v>
       </c>
-      <c r="L37">
+      <c r="L37" t="n">
         <v>1939.2152</v>
       </c>
-      <c r="M37">
+      <c r="M37" t="n">
         <v>1900.7365</v>
       </c>
-      <c r="N37">
+      <c r="N37" t="n">
         <v>1808.017</v>
       </c>
-      <c r="O37">
+      <c r="O37" t="n">
         <v>1651.8266</v>
       </c>
-      <c r="P37">
+      <c r="P37" t="n">
         <v>1653.5912</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" t="n">
         <v>1644.5197</v>
       </c>
-      <c r="R37">
+      <c r="R37" t="n">
         <v>1563.7283</v>
       </c>
-      <c r="S37">
+      <c r="S37" t="n">
         <v>1454.8496</v>
       </c>
-      <c r="T37">
+      <c r="T37" t="n">
         <v>1193.9358</v>
       </c>
+      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>